--- a/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -387,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +435,9 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3826" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="31">
   <si>
     <t>ID</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t>Dawes Rolls Full Document - Creek By Blood - Page 627</t>
+  </si>
+  <si>
+    <t>Image Name</t>
+  </si>
+  <si>
+    <t>Image Binary</t>
   </si>
 </sst>
 </file>
@@ -432,14 +438,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1900"/>
+  <dimension ref="A1:Q1900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="14" max="14" width="51.140625" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -485,8 +493,14 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -503,7 +517,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -523,7 +537,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:17">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -543,7 +557,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -563,7 +577,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -583,7 +597,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -603,7 +617,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -623,7 +637,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -643,7 +657,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -663,7 +677,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -683,7 +697,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -703,7 +717,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -723,7 +737,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -743,7 +757,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -763,7 +777,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>

--- a/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3900" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -107,6 +107,12 @@
   </si>
   <si>
     <t>Image Binary</t>
+  </si>
+  <si>
+    <t>Stricken from roll</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -3067,8 +3073,35 @@
         <f t="shared" si="6"/>
         <v>616</v>
       </c>
+      <c r="D130" t="s">
+        <v>31</v>
+      </c>
+      <c r="E130" t="s">
+        <v>32</v>
+      </c>
+      <c r="F130" t="s">
+        <v>32</v>
+      </c>
+      <c r="G130" t="s">
+        <v>32</v>
+      </c>
+      <c r="H130">
+        <v>-1</v>
+      </c>
+      <c r="I130" t="s">
+        <v>32</v>
+      </c>
+      <c r="J130" t="s">
+        <v>32</v>
+      </c>
+      <c r="K130" t="s">
+        <v>32</v>
+      </c>
       <c r="L130" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="M130" t="s">
+        <v>32</v>
       </c>
       <c r="N130" t="str">
         <f t="shared" si="7"/>
@@ -3087,8 +3120,35 @@
         <f t="shared" si="6"/>
         <v>616</v>
       </c>
+      <c r="D131" t="s">
+        <v>31</v>
+      </c>
+      <c r="E131" t="s">
+        <v>32</v>
+      </c>
+      <c r="F131" t="s">
+        <v>32</v>
+      </c>
+      <c r="G131" t="s">
+        <v>32</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131" t="s">
+        <v>32</v>
+      </c>
+      <c r="J131" t="s">
+        <v>32</v>
+      </c>
+      <c r="K131" t="s">
+        <v>32</v>
+      </c>
       <c r="L131" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="M131" t="s">
+        <v>32</v>
       </c>
       <c r="N131" t="str">
         <f t="shared" si="7"/>
@@ -4107,8 +4167,35 @@
         <f t="shared" si="9"/>
         <v>616</v>
       </c>
+      <c r="D182" t="s">
+        <v>31</v>
+      </c>
+      <c r="E182" t="s">
+        <v>32</v>
+      </c>
+      <c r="F182" t="s">
+        <v>32</v>
+      </c>
+      <c r="G182" t="s">
+        <v>32</v>
+      </c>
+      <c r="H182">
+        <v>-1</v>
+      </c>
+      <c r="I182" t="s">
+        <v>32</v>
+      </c>
+      <c r="J182" t="s">
+        <v>32</v>
+      </c>
+      <c r="K182" t="s">
+        <v>32</v>
+      </c>
       <c r="L182" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="M182" t="s">
+        <v>32</v>
       </c>
       <c r="N182" t="str">
         <f t="shared" si="10"/>
@@ -4945,8 +5032,35 @@
         <f t="shared" si="11"/>
         <v>617</v>
       </c>
+      <c r="D224" t="s">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>32</v>
+      </c>
+      <c r="F224" t="s">
+        <v>32</v>
+      </c>
+      <c r="G224" t="s">
+        <v>32</v>
+      </c>
+      <c r="H224">
+        <v>-1</v>
+      </c>
+      <c r="I224" t="s">
+        <v>32</v>
+      </c>
+      <c r="J224" t="s">
+        <v>32</v>
+      </c>
+      <c r="K224" t="s">
+        <v>32</v>
+      </c>
       <c r="L224" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="M224" t="s">
+        <v>32</v>
       </c>
       <c r="N224" t="str">
         <f t="shared" si="12"/>
@@ -4965,8 +5079,35 @@
         <f t="shared" si="11"/>
         <v>617</v>
       </c>
+      <c r="D225" t="s">
+        <v>31</v>
+      </c>
+      <c r="E225" t="s">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>32</v>
+      </c>
+      <c r="G225" t="s">
+        <v>32</v>
+      </c>
+      <c r="H225">
+        <v>-1</v>
+      </c>
+      <c r="I225" t="s">
+        <v>32</v>
+      </c>
+      <c r="J225" t="s">
+        <v>32</v>
+      </c>
+      <c r="K225" t="s">
+        <v>32</v>
+      </c>
       <c r="L225" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="M225" t="s">
+        <v>32</v>
       </c>
       <c r="N225" t="str">
         <f t="shared" si="12"/>
@@ -4985,8 +5126,35 @@
         <f t="shared" si="11"/>
         <v>617</v>
       </c>
+      <c r="D226" t="s">
+        <v>31</v>
+      </c>
+      <c r="E226" t="s">
+        <v>32</v>
+      </c>
+      <c r="F226" t="s">
+        <v>32</v>
+      </c>
+      <c r="G226" t="s">
+        <v>32</v>
+      </c>
+      <c r="H226">
+        <v>-1</v>
+      </c>
+      <c r="I226" t="s">
+        <v>32</v>
+      </c>
+      <c r="J226" t="s">
+        <v>32</v>
+      </c>
+      <c r="K226" t="s">
+        <v>32</v>
+      </c>
       <c r="L226" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="M226" t="s">
+        <v>32</v>
       </c>
       <c r="N226" t="str">
         <f t="shared" si="12"/>
@@ -22255,8 +22423,35 @@
         <f t="shared" si="55"/>
         <v>622</v>
       </c>
+      <c r="D1090" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1090" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1090" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1090">
+        <v>-1</v>
+      </c>
+      <c r="I1090" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1090" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1090" t="s">
+        <v>32</v>
+      </c>
       <c r="L1090" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="M1090" t="s">
+        <v>32</v>
       </c>
       <c r="N1090" t="str">
         <f t="shared" si="56"/>
@@ -30971,8 +31166,35 @@
         <f t="shared" si="78"/>
         <v>624</v>
       </c>
+      <c r="D1526" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1526" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1526" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1526" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1526">
+        <v>-1</v>
+      </c>
+      <c r="I1526" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1526" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1526" t="s">
+        <v>32</v>
+      </c>
       <c r="L1526" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="M1526" t="s">
+        <v>32</v>
       </c>
       <c r="N1526" t="str">
         <f t="shared" si="79"/>
@@ -30991,8 +31213,35 @@
         <f t="shared" si="78"/>
         <v>624</v>
       </c>
+      <c r="D1527" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1527" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1527" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1527" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1527">
+        <v>-1</v>
+      </c>
+      <c r="I1527" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1527" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1527" t="s">
+        <v>32</v>
+      </c>
       <c r="L1527" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="M1527" t="s">
+        <v>32</v>
       </c>
       <c r="N1527" t="str">
         <f t="shared" si="79"/>

--- a/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3900" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3901" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -103,16 +103,19 @@
     <t>Dawes Rolls Full Document - Creek By Blood - Page 627</t>
   </si>
   <si>
-    <t>Image Name</t>
-  </si>
-  <si>
-    <t>Image Binary</t>
-  </si>
-  <si>
     <t>Stricken from roll</t>
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>ImageBinary</t>
+  </si>
+  <si>
+    <t>ImageName</t>
+  </si>
+  <si>
+    <t>TribeRelationship</t>
   </si>
 </sst>
 </file>
@@ -444,16 +447,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q1900"/>
+  <dimension ref="A1:R1900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="14" max="14" width="51.140625" customWidth="1"/>
     <col min="16" max="16" width="15.28515625" customWidth="1"/>
     <col min="17" max="17" width="18.42578125" customWidth="1"/>
+    <col min="18" max="18" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -500,13 +504,16 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+        <v>31</v>
+      </c>
+      <c r="R1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -523,7 +530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -543,7 +550,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -563,7 +570,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -583,7 +590,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -603,7 +610,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -623,7 +630,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -643,7 +650,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -663,7 +670,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -683,7 +690,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -703,7 +710,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -723,7 +730,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -743,7 +750,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -763,7 +770,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -783,7 +790,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 615</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3074,34 +3081,34 @@
         <v>616</v>
       </c>
       <c r="D130" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H130">
         <v>-1</v>
       </c>
       <c r="I130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N130" t="str">
         <f t="shared" si="7"/>
@@ -3121,34 +3128,34 @@
         <v>616</v>
       </c>
       <c r="D131" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E131" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F131" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G131" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H131">
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J131" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K131" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L131" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M131" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N131" t="str">
         <f t="shared" si="7"/>
@@ -4168,34 +4175,34 @@
         <v>616</v>
       </c>
       <c r="D182" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E182" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F182" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G182" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H182">
         <v>-1</v>
       </c>
       <c r="I182" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J182" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K182" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L182" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M182" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N182" t="str">
         <f t="shared" si="10"/>
@@ -5033,34 +5040,34 @@
         <v>617</v>
       </c>
       <c r="D224" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E224" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F224" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G224" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H224">
         <v>-1</v>
       </c>
       <c r="I224" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J224" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K224" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L224" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M224" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N224" t="str">
         <f t="shared" si="12"/>
@@ -5080,34 +5087,34 @@
         <v>617</v>
       </c>
       <c r="D225" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E225" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F225" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G225" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H225">
         <v>-1</v>
       </c>
       <c r="I225" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J225" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K225" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L225" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M225" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N225" t="str">
         <f t="shared" si="12"/>
@@ -5127,34 +5134,34 @@
         <v>617</v>
       </c>
       <c r="D226" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E226" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F226" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G226" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H226">
         <v>-1</v>
       </c>
       <c r="I226" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J226" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K226" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L226" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M226" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N226" t="str">
         <f t="shared" si="12"/>
@@ -22424,34 +22431,34 @@
         <v>622</v>
       </c>
       <c r="D1090" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E1090" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F1090" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G1090" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H1090">
         <v>-1</v>
       </c>
       <c r="I1090" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J1090" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K1090" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L1090" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M1090" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N1090" t="str">
         <f t="shared" si="56"/>
@@ -31167,34 +31174,34 @@
         <v>624</v>
       </c>
       <c r="D1526" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E1526" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F1526" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G1526" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H1526">
         <v>-1</v>
       </c>
       <c r="I1526" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J1526" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K1526" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L1526" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M1526" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N1526" t="str">
         <f t="shared" si="79"/>
@@ -31214,34 +31221,34 @@
         <v>624</v>
       </c>
       <c r="D1527" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E1527" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F1527" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G1527" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H1527">
         <v>-1</v>
       </c>
       <c r="I1527" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J1527" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K1527" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L1527" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M1527" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N1527" t="str">
         <f t="shared" si="79"/>
